--- a/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H294"/>
+  <dimension ref="A1:H308"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け……納得はしておりません。</t>
+          <t xml:space="preserve">このままでは、納得しておりません。</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.ojousama[1]</t>
+          <t xml:space="preserve">accepted.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…えぇ、もう少しだけ続けてみますわ</t>
+          <t xml:space="preserve">…いろいろと、ありがとうございました。新しい場所でも、闘い続けますわ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">accepted.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しだけ…あのベルトに手を伸ばしたいですわ</t>
+          <t xml:space="preserve">ここで過ごした日々を、忘れることはございません</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">defended.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ使い道がおありですのね。お付き合いしてさしあげますわ</t>
+          <t xml:space="preserve">…ここに残れて、ほっといたしましたわ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">defended.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたがそうおっしゃるなら…もう少しだけ頑張りますわ</t>
+          <t xml:space="preserve">社長…ありがとうございます。ご期待には応えます</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後によい試合をさせてください</t>
+          <t xml:space="preserve">…申し訳ございません。新しい場所で、答えを出しますわ</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…言われなくても、辞めるつもりでしたわ</t>
+          <t xml:space="preserve">お世話になりました。…またいずれ、どこかで</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.ojousama[1]</t>
+          <t xml:space="preserve">default.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりましたわ。潮時ですわね</t>
+          <t xml:space="preserve">…えぇ、もう少しだけ続けてみますわ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.ojousama[1]</t>
+          <t xml:space="preserve">former_champ.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりましたわ。もう限界ですもの</t>
+          <t xml:space="preserve">もう少しだけ…あのベルトに手を伸ばしたいですわ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.ojousama[1]</t>
+          <t xml:space="preserve">heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですわね。最近、勝てませんでしたもの</t>
+          <t xml:space="preserve">まだ使い道がおありですのね。お付き合いしてさしあげますわ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">high_trust.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに引退ですって？ ご冗談を</t>
+          <t xml:space="preserve">あなたがそうおっしゃるなら…もう少しだけ頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_former_champ.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3695,14 +3695,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを追い出すおつもり？ そうはいきませんわ</t>
+          <t xml:space="preserve">最後によい試合をさせてください</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わりませんわ。わたくしはまだ闘えます</t>
+          <t xml:space="preserve">…言われなくても、辞めるつもりでしたわ</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_no_title.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引退ですって？ 次の興行をご覧になってくださいまし</t>
+          <t xml:space="preserve">…わかりましたわ。潮時ですわね</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_terminal.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点の景色…一生忘れない</t>
+          <t xml:space="preserve">…わかりましたわ。もう限界ですもの</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_winless.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトには届きませんでした。でも、後悔はありません</t>
+          <t xml:space="preserve">…そうですわね。最近、勝てませんでしたもの</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_champ.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3855,14 +3855,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お泣きにならないで。みっともなくてよ</t>
+          <t xml:space="preserve">チャンピオンに引退ですって？ ご冗談を</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_distrust.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが、わたくしの全てでしたわ</t>
+          <t xml:space="preserve">わたくしを追い出すおつもり？ そうはいきませんわ</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_fighting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ何も…成し遂げていませんのに…</t>
+          <t xml:space="preserve">まだ終わりませんわ。わたくしはまだ闘えます</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がね…もう言うことを聞かないの…</t>
+          <t xml:space="preserve">引退ですって？ 次の興行をご覧になってくださいまし</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.ojousama[1]</t>
+          <t xml:space="preserve">A1_champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかっておりましたわ。いつか来ると</t>
+          <t xml:space="preserve">頂点の景色…一生忘れない</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト…まだ返したくはなかった</t>
+          <t xml:space="preserve">ベルトには届きませんでした。でも、後悔はありません</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくし、こちらに残らせていただきますわ。ここが一番輝ける場所ですもの</t>
+          <t xml:space="preserve">お泣きにならないで。みっともなくてよ</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4064,29 +4064,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。より一層、精進いたしますわね。</t>
+          <t xml:space="preserve">ここが、わたくしの全てでしたわ</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4096,29 +4096,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そのお気持ちだけでも、嬉しいわ。</t>
+          <t xml:space="preserve">まだ何も…成し遂げていませんのに…</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4128,29 +4128,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……左様ですか。承知いたしました。</t>
+          <t xml:space="preserve">体がね…もう言うことを聞かないの…</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4160,29 +4160,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お時間よろしいかしら。{tenure}待遇について、ご相談させてください。{record}</t>
+          <t xml:space="preserve">わかっておりましたわ。いつか来ると</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4192,29 +4192,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうですか。承知いたしました……。</t>
+          <t xml:space="preserve">このベルト…まだ返したくはなかった</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4224,29 +4224,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お耳を傾けてくださるのね。{record}新たな場所で己を試したいのです。</t>
+          <t xml:space="preserve">わたくし、こちらに残らせていただきますわ。ここが一番輝ける場所ですもの</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}お伝えしづらいのですが…退団を考えておりますの。</t>
+          <t xml:space="preserve">ありがとうございますわ。より一層、精進いたしますわね。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。{tenure_farewell}{rivalry}ごきげんよう。</t>
+          <t xml:space="preserve">……そのお気持ちだけでも、嬉しいわ。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お気持ちは嬉しいのですが…もう、決めました。</t>
+          <t xml:space="preserve">……左様ですか。承知いたしました。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4367,433 +4367,433 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまでおっしゃるなら。もう少しお付き合いいたします。</t>
+          <t xml:space="preserve">社長、お時間よろしいかしら。{tenure}待遇について、ご相談させてください。{record}</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そうですか。承知いたしました……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、要点だけ申し上げます。辞めます。もう決めましたの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お世話になりました。ですが、もうここに留まることはできません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お耳を傾けてくださるのね。{record}新たな場所で己を試したいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}お伝えしづらいのですが…退団を考えておりますの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしました。{tenure_farewell}{rivalry}ごきげんよう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お気持ちは嬉しいのですが…もう、決めました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そこまでおっしゃるなら。もう少しお付き合いいたします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D136" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F136" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">大変恐縮ですが、そのようなお話は伺えませんわ。
 今の団体への思いは揺らぎませんの</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr" s="12">
+      <c r="D137" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr" s="2">
+      <c r="E137" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr" s="3">
+      <c r="F137" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">申し訳ありませんが、今回はご遠慮しますわ</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr" s="12">
+      <c r="D138" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr" s="2">
+      <c r="E138" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr" s="3">
+      <c r="F138" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしをお誘いですの？
 …条件次第ですわね</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr" s="12">
+      <c r="D139" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr" s="2">
+      <c r="E139" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr" s="3">
+      <c r="F139" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…承知しましたわ。
 実力で居場所を作ってみせます</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">率直に申し上げます。このままでは、わたくしたちは朽ちますわ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">何かが変わった気がいたします…壁を越えたのね</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">（…体が軽いわ。何かが変わったかしら——）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここが限界…でも、ここまで来られたことに感謝ですわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="40" customHeight="1">
-      <c r="A136" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来れたのですね…感慨深いですわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="40" customHeight="1">
-      <c r="A137" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">確かに成長を感じますわ。…まだまだですけれど</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="40" customHeight="1">
-      <c r="A138" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">この領域に立てたのは…光栄ですわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="40" customHeight="1">
-      <c r="A139" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_growth.normal.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">わたくしのことを知ってくださる方が増えましたわ</t>
-        </is>
-      </c>
-    </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これだけの方に応援いただけるなんて…身が引き締まりますわ</t>
+          <t xml:space="preserve">率直に申し上げます。このままでは、わたくしたちは朽ちますわ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
@@ -4818,14 +4818,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何のために…闘っているのかしら、わたし</t>
+          <t xml:space="preserve">何かが変わった気がいたします…壁を越えたのね</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
@@ -4850,14 +4850,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…やれるわ。やって見せる</t>
+          <t xml:space="preserve">（…体が軽いわ。何かが変わったかしら——）</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">cap_reached.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4882,14 +4882,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…戻ってこれましたわ</t>
+          <t xml:space="preserve">ここが限界…でも、ここまで来られたことに感謝ですわ</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.ojousama[1]</t>
+          <t xml:space="preserve">ovr_elite.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの敗北から…何かがおかしい気がする</t>
+          <t xml:space="preserve">ここまで来れたのですね…感慨深いですわ</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">ovr_growth.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4946,14 +4946,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治りったのに…動けない……なぜ？</t>
+          <t xml:space="preserve">確かに成長を感じますわ。…まだまだですけれど</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">ovr_legend.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4978,14 +4978,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに戻れたというのに…怖いわ</t>
+          <t xml:space="preserve">この領域に立てたのは…光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.ojousama[1]</t>
+          <t xml:space="preserve">pop_growth.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5010,14 +5010,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は癒えましたのに…気力が戻ないわね</t>
+          <t xml:space="preserve">わたくしのことを知ってくださる方が増えましたわ</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5027,29 +5027,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">pop_star.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あのような激闘、生涯忘れませんわ。対戦してくれたお相手に、心より敬意を</t>
+          <t xml:space="preserve">これだけの方に応援いただけるなんて…身が引き締まりますわ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5059,29 +5059,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この王座をお預かりしている限り、最高の試合をお約束いたします</t>
+          <t xml:space="preserve">何のために…闘っているのかしら、わたし</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5091,29 +5091,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">華やかな舞台から降りる日が来たということ。…でも、後悔はございません</t>
+          <t xml:space="preserve">まだ…やれるわ。やって見せる</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5123,29 +5123,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">光栄でございます。また精進いたします</t>
+          <t xml:space="preserve">ようやく…戻ってこれましたわ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5155,29 +5155,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.ojousama[1]</t>
+          <t xml:space="preserve">defeat.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年を通して成長できましたこと、皆さまのおかげです</t>
+          <t xml:space="preserve">あの敗北から…何かがおかしい気がする</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5187,29 +5187,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.ojousama[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさかわたくしがこのような栄誉に…。先輩方の背中、しかと見ておりました</t>
+          <t xml:space="preserve">体は治りったのに…動けない……なぜ？</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5219,29 +5219,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングに立てますこと、身に余る光栄ですわ</t>
+          <t xml:space="preserve">リングに戻れたというのに…怖いわ</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5251,29 +5251,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">penalty_end.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このような大舞台、夢にまで見ましたのよ</t>
+          <t xml:space="preserve">怪我は癒えましたのに…気力が戻ないわね</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">bestMatch.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日を、生涯忘れませんわ</t>
+          <t xml:space="preserve">あのような激闘、生涯忘れませんわ。対戦してくれたお相手に、心より敬意を</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5330,14 +5330,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員御礼、まさに奇跡のような景色ですわ…</t>
+          <t xml:space="preserve">この王座をお預かりしている限り、最高の試合をお約束いたします</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">hallOfFame.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5362,14 +5362,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の熱気、今も胸に残っておりますの</t>
+          <t xml:space="preserve">華やかな舞台から降りる日が来たということ。…でも、後悔はございません</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">mediaAward.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この日のこと、生涯の誇りとしますわ</t>
+          <t xml:space="preserve">光栄でございます。また精進いたします</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5411,29 +5411,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.ojousama[1]</t>
+          <t xml:space="preserve">mvp.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">稽古が楽しくなってまいりました</t>
+          <t xml:space="preserve">一年を通して成長できましたこと、皆さまのおかげです</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.ojousama[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5443,29 +5443,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.ojousama[2]</t>
+          <t xml:space="preserve">rookie.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しずつ、体が応えてくれるようになってきたわね</t>
+          <t xml:space="preserve">まさかわたくしがこのような栄誉に…。先輩方の背中、しかと見ておりました</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5475,29 +5475,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い仲間に恵まれたわね</t>
+          <t xml:space="preserve">ドームのリングに立てますこと、身に余る光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5507,29 +5507,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少々疲れが出たようで…次までには整えます</t>
+          <t xml:space="preserve">このような大舞台、夢にまで見ましたのよ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[3]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5539,29 +5539,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[3]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様からこれほどの声援をいただけるのは、光栄です</t>
+          <t xml:space="preserve">今日という日を、生涯忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5571,29 +5571,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう結構ですわ</t>
+          <t xml:space="preserve">満員御礼、まさに奇跡のような景色ですわ…</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5603,29 +5603,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、考え事がございまして</t>
+          <t xml:space="preserve">お客様の熱気、今も胸に残っておりますの</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[3]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5635,29 +5635,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[3]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お金のことで文句を言うつもりはないけれど</t>
+          <t xml:space="preserve">この日のこと、生涯の誇りとしますわ</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5667,29 +5667,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.ojousama[1]</t>
+          <t xml:space="preserve">N1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ。……わたくし、この程度に見られていましたのね</t>
+          <t xml:space="preserve">稽古が楽しくなってまいりました</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5699,29 +5699,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.ojousama[1]</t>
+          <t xml:space="preserve">N1.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、ありがとうございます。大切に使わせていただきます</t>
+          <t xml:space="preserve">少しずつ、体が応えてくれるようになってきたわね</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5731,29 +5731,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.ojousama[1]</t>
+          <t xml:space="preserve">N2.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿ですの？ 精一杯取り組みますわ</t>
+          <t xml:space="preserve">良い仲間に恵まれたわね</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5763,29 +5763,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">N3.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見守ってくださったんですのね…その気持ちに、お応えしなくては</t>
+          <t xml:space="preserve">少々疲れが出たようで…次までには整えます</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.ojousama[1]</t>
+          <t xml:space="preserve">N4.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。もう少し、頑張ってみます</t>
+          <t xml:space="preserve">皆様からこれほどの声援をいただけるのは、光栄です</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5827,29 +5827,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.ojousama[1]</t>
+          <t xml:space="preserve">N5_low.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアのお仕事ですの？ 精一杯務めます</t>
+          <t xml:space="preserve">…もう結構ですわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5859,29 +5859,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.ojousama[1]</t>
+          <t xml:space="preserve">N5_warning.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しいお時間でしたわ。それでは、ごきげんよう</t>
+          <t xml:space="preserve">…少し、考え事がございまして</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5891,29 +5891,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.ojousama[1]</t>
+          <t xml:space="preserve">G1.voice.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。リフレッシュして戻って参ります</t>
+          <t xml:space="preserve">…お金のことで文句を言うつもりはないけれど</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.ojousama[1]</t>
+          <t xml:space="preserve">bonus_insult.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5938,14 +5938,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…そこまでしてくださるなんて。早く戻りますわ</t>
+          <t xml:space="preserve">まあ。……わたくし、この程度に見られていましたのね</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.ojousama[1]</t>
+          <t xml:space="preserve">bonus.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5970,14 +5970,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯、学ばせていただきます</t>
+          <t xml:space="preserve">まあ、ありがとうございます。大切に使わせていただきます</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.ojousama[1]</t>
+          <t xml:space="preserve">camp.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアのお話ですの？ ぜひお受けしたいですわ</t>
+          <t xml:space="preserve">合宿ですの？ 精一杯取り組みますわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.ojousama[1]</t>
+          <t xml:space="preserve">encourage_high_trust.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6034,14 +6034,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からお話がございましたの…</t>
+          <t xml:space="preserve">ずっと見守ってくださったんですのね…その気持ちに、お応えしなくては</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.ojousama[1]</t>
+          <t xml:space="preserve">encourage.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6066,14 +6066,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はお稽古をお休みさせていただきますわ…理由は…ご想像にお任せしますわ</t>
+          <t xml:space="preserve">…ありがとうございます。もう少し、頑張ってみます</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.ojousama[1]</t>
+          <t xml:space="preserve">media.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6098,14 +6098,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（控室で「あの方の采配、少しおかしくなくて？」と囁いている）</t>
+          <t xml:space="preserve">メディアのお仕事ですの？ 精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.ojousama[1]</t>
+          <t xml:space="preserve">party.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「窮屈な場所からは、いつでも出ていけますの」と投稿）</t>
+          <t xml:space="preserve">楽しいお時間でしたわ。それでは、ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.ojousama[1]</t>
+          <t xml:space="preserve">refresh_leave.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座への挑戦をお許しいただけませんこと？</t>
+          <t xml:space="preserve">ありがとうございます。リフレッシュして戻って参ります</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.ojousama[1]</t>
+          <t xml:space="preserve">special_treatment.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6194,14 +6194,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方との決着を、お許しいただけませんか？</t>
+          <t xml:space="preserve">まあ…そこまでしてくださるなんて。早く戻りますわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.ojousama[1]</t>
+          <t xml:space="preserve">trainer.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6226,14 +6226,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお休みをいただけますかしら…</t>
+          <t xml:space="preserve">精一杯、学ばせていただきます</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.ojousama[1]</t>
+          <t xml:space="preserve">E1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは困ります！お話し合いをさせてくださいまし</t>
+          <t xml:space="preserve">メディアのお話ですの？ ぜひお受けしたいですわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.ojousama[1]</t>
+          <t xml:space="preserve">E4.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓の時間をいただけませんこと？</t>
+          <t xml:space="preserve">新しいスカウトのお話が、届いているそうです</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.ojousama[1]</t>
+          <t xml:space="preserve">E6.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6322,14 +6322,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩のお世話は、私にお任せください</t>
+          <t xml:space="preserve">他の団体からお話がございましたの…</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6354,14 +6354,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお時間をいただくことになりそうですわ…</t>
+          <t xml:space="preserve">今日はお稽古をお休みさせていただきますわ…理由は…ご想像にお任せしますわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.ojousama[1]</t>
+          <t xml:space="preserve">S_grumble.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…もう限界ですわ</t>
+          <t xml:space="preserve">（控室で「あの方の采配、少しおかしくなくて？」と囁いている）</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.ojousama[1]</t>
+          <t xml:space="preserve">S_sns.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6418,14 +6418,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちらにも非がおありでしょうに…</t>
+          <t xml:space="preserve">（SNSに「窮屈な場所からは、いつでも出ていけますの」と投稿）</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.ojousama[1]</t>
+          <t xml:space="preserve">S1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6450,14 +6450,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、コラボのお話ですの。嬉しい限りですわ</t>
+          <t xml:space="preserve">王座への挑戦をお許しいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.ojousama[1]</t>
+          <t xml:space="preserve">S2.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMですか。しっかりお役目を果たしますわ</t>
+          <t xml:space="preserve">あの方との決着を、お許しいただけませんか？</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal.ojousama[1]</t>
+          <t xml:space="preserve">S3.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に直接お礼を申し上げる機会ですわね</t>
+          <t xml:space="preserve">少しお休みをいただけますかしら…</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal.ojousama[1]</t>
+          <t xml:space="preserve">S4_direct.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイですか。精一杯美しく歩いてみせますわ</t>
+          <t xml:space="preserve">このままでは困ります！お話し合いをさせてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.ojousama[1]</t>
+          <t xml:space="preserve">S4_silent.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6578,14 +6578,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">撮影ですか。美しく仕上げていただけるよう努めますわ</t>
+          <t xml:space="preserve">（…申し上げたいことは、ございます。けれど、口にはできません）</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.ojousama[1]</t>
+          <t xml:space="preserve">S5.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6610,14 +6610,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ番組ですか。品よくふるまえるよう努めますわ</t>
+          <t xml:space="preserve">特訓の時間をいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.ojousama[1]</t>
+          <t xml:space="preserve">S6.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材ですか？ 精一杯務めさせていただきます</t>
+          <t xml:space="preserve">後輩のお世話は、私にお任せください</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6659,29 +6659,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">B1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
+          <t xml:space="preserve">少しお時間をいただくことになりそうですわ…</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6691,29 +6691,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter1.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
+          <t xml:space="preserve">あの方とは…もう限界ですわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6723,29 +6723,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">B2_fighter2.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
+          <t xml:space="preserve">あちらにも非がおありでしょうに…</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6755,29 +6755,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_brand.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
+          <t xml:space="preserve">まあ、コラボのお話ですの。嬉しい限りですわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6787,29 +6787,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_cm.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
+          <t xml:space="preserve">CMですか。しっかりお役目を果たしますわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6819,29 +6819,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_fan.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
+          <t xml:space="preserve">ファンの方々に直接お礼を申し上げる機会ですわね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6851,29 +6851,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">B4_fashion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
+          <t xml:space="preserve">ランウェイですか。精一杯美しく歩いてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6883,29 +6883,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_gravure.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
+          <t xml:space="preserve">撮影ですか。美しく仕上げていただけるよう努めますわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_variety.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
+          <t xml:space="preserve">バラエティ番組ですか。品よくふるまえるよう努めますわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6947,29 +6947,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.ojousama[2]</t>
+          <t xml:space="preserve">B4.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
+          <t xml:space="preserve">取材ですか？ 精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6994,14 +6994,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
+          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7026,14 +7026,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
+          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7058,14 +7058,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.ojousama[2]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7090,14 +7090,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7122,14 +7122,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.ojousama[2]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7154,14 +7154,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
+          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7186,14 +7186,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
+          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
+          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7250,14 +7250,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
+          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7282,14 +7282,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">faGreeting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7314,14 +7314,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンですわ…！夢のようですわね…！</t>
+          <t xml:space="preserve">行くあての無いわたくしを招いてくださって。恩は必ずお返しします</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7346,14 +7346,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">faWelcome.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">injury.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7410,14 +7410,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
+          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">injury.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
+          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">release.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
+          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">release.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
+          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">rentalGreeting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンですわ…！夢のようですわね…！</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7555,29 +7555,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">scoutGreeting.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう以前のようには戻れませんわ</t>
+          <t xml:space="preserve">わたくしを見つけたご慧眼、称えて差し上げます</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7587,29 +7587,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し距離ができたように感じますわ</t>
+          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7619,29 +7619,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleDefense.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不思議と波長が合いますの。心地よい距離感ですわ</t>
+          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7651,29 +7651,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleLoss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">かけがえのない方ですわ。何物にも代えられません</t>
+          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7683,29 +7683,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう過去のことですわ</t>
+          <t xml:space="preserve">チャンピオンですわ…！夢のようですわね…！</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7715,29 +7715,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくありませんわ…こんな気持ちは初めて</t>
+          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7747,29 +7747,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何としてでも超えてみせますわ</t>
+          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7779,29 +7779,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの宿命ですわ…それ以外に言葉がない</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7811,29 +7811,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここがわたくしの居場所ですわ。誇りに思います</t>
+          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7843,29 +7843,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このような扱いを受ける覚えはございませんわ</t>
+          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7875,29 +7875,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の運営方針に…疑問を感じますわ</t>
+          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7907,29 +7907,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">敗北は悔しいですけど…素晴らしい試合でした</t>
+          <t xml:space="preserve">チャンピオンですわ…！夢のようですわね…！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7954,14 +7954,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素晴らしい勝利ですわ。この舞台に相応しい試合でした</t>
+          <t xml:space="preserve">もう以前のようには戻れませんわ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7986,14 +7986,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この敗北…受け入れがたいわね</t>
+          <t xml:space="preserve">少し距離ができたように感じますわ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8018,14 +8018,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利。当然の結果ですけどね</t>
+          <t xml:space="preserve">不思議と波長が合いますの。心地よい距離感ですわ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8050,14 +8050,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
+          <t xml:space="preserve">かけがえのない方ですわ。何物にも代えられません</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
+          <t xml:space="preserve">もう過去のことですわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8114,14 +8114,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待遇には満足しております</t>
+          <t xml:space="preserve">負けたくありませんわ…こんな気持ちは初めて</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8146,14 +8146,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
+          <t xml:space="preserve">何としてでも超えてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8178,14 +8178,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動向が…気になります</t>
+          <t xml:space="preserve">わたくしの宿命ですわ…それ以外に言葉がない</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.ojousama[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8210,14 +8210,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
+          <t xml:space="preserve">ここがわたくしの居場所ですわ。誇りに思います</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8242,14 +8242,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調が…あまり芳しくありません</t>
+          <t xml:space="preserve">このような扱いを受ける覚えはございませんわ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8274,14 +8274,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
+          <t xml:space="preserve">この団体の運営方針に…疑問を感じますわ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8306,14 +8306,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
+          <t xml:space="preserve">敗北は悔しいですけど…素晴らしい試合でした</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8338,14 +8338,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
+          <t xml:space="preserve">素晴らしい勝利ですわ。この舞台に相応しい試合でした</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.loss.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8370,14 +8370,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
+          <t xml:space="preserve">この敗北…受け入れがたいわね</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.win.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8402,14 +8402,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
+          <t xml:space="preserve">勝利。当然の結果ですけどね</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8419,29 +8419,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-02.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
+          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8451,29 +8451,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">GL-03.down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
+          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8483,29 +8483,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-03.up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
+          <t xml:space="preserve">待遇には満足しております</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8515,29 +8515,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">GL-04.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
+          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8547,29 +8547,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-05.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お見送りしましたわ。…息は乱れていますけれど、退きませんの。次はどなた?</t>
+          <t xml:space="preserve">動向が…気になります</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8579,29 +8579,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.ojousama[2]</t>
+          <t xml:space="preserve">GL-06.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだこのリングに立っていますのよ。次の方、早くいらして</t>
+          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8611,29 +8611,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-07.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはなりませんの</t>
+          <t xml:space="preserve">体調が…あまり芳しくありません</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8643,29 +8643,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">GL-08.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
+          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8675,29 +8675,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-09.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりませんの</t>
+          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8707,29 +8707,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.ojousama[2]</t>
+          <t xml:space="preserve">GL-10.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞だけでは、わたくし、満足できませんわ。次は三人で勝ちますの</t>
+          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8739,29 +8739,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-11.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お身体はもう悲鳴を上げていますわ。ですが……このリングを明け渡す理由にはなりませんの</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8771,29 +8771,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.ojousama[2]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
+          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8803,12 +8803,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8818,14 +8818,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
+          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">preFinal.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8850,14 +8850,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
+          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8882,14 +8882,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
+          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8914,14 +8914,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
+          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">survivor.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
+          <t xml:space="preserve">一人、お見送りしましたわ。…息は乱れていますけれど、退きませんの。次はどなた?</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">survivor.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8978,14 +8978,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次もこの調子で参ります</t>
+          <t xml:space="preserve">まだこのリングに立っていますのよ。次の方、早くいらして</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9010,14 +9010,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
+          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはなりませんの</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">champion.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9042,14 +9042,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実りある大会でした</t>
+          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">defiant.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝。全てを出し切ります</t>
+          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりませんの</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">defiant.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
+          <t xml:space="preserve">この賞だけでは、わたくし、満足できませんわ。次は三人で勝ちますの</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">gauntlet.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
+          <t xml:space="preserve">お身体はもう悲鳴を上げていますわ。ですが……このリングを明け渡す理由にはなりませんの</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">gauntlet.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
+          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.ojousama[1]</t>
+          <t xml:space="preserve">champion.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9202,14 +9202,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
+          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.ojousama[2]</t>
+          <t xml:space="preserve">champion.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9234,14 +9234,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
+          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">postLose.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
+          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">postLose.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9298,14 +9298,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
+          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">postMatchWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9330,14 +9330,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
+          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">postMatchWin.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、こちらの団体さん？ 随分とかわいらしい興行をなさっていますわね</t>
+          <t xml:space="preserve">次もこの調子で参ります</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">postWin.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
+          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">postWin.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9426,14 +9426,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
+          <t xml:space="preserve">実りある大会でした</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">preFinal.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9458,14 +9458,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
+          <t xml:space="preserve">決勝。全てを出し切ります</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9475,12 +9475,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
+          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
+          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
+          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.ojousama[2]</t>
+          <t xml:space="preserve">summon.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9586,14 +9586,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
+          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">summon.normal.ojousama[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
+          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9650,14 +9650,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
+          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9682,44 +9682,492 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
+          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、こちらの団体さん？ 随分とかわいらしい興行をなさっていますわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr" s="2">
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr" s="12">
+      <c r="D306" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.normal.ojousama[1]</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr" s="2">
+      <c r="E306" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr" s="3">
+      <c r="F306" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここまで来れたのね…感無量だわ</t>
         </is>
       </c>
     </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">行くあての無いわたくしを招いてくださって。恩は必ずお返しします</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしを見つけたご慧眼、称えて差し上げます</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H294"/>
+  <autoFilter ref="A1:H308"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
@@ -342,7 +342,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -357,7 +357,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.ojousama[1]</t>
+          <t xml:space="preserve">atk.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -374,7 +374,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -389,7 +389,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.ojousama[2]</t>
+          <t xml:space="preserve">atk.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -406,7 +406,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -421,7 +421,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.ojousama[3]</t>
+          <t xml:space="preserve">atk.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -438,7 +438,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.ojousama[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -453,7 +453,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.ojousama[4]</t>
+          <t xml:space="preserve">atk.ojousama.normal[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -470,7 +470,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -485,7 +485,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.ojousama[1]</t>
+          <t xml:space="preserve">bigmove.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -502,7 +502,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -517,7 +517,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.ojousama[2]</t>
+          <t xml:space="preserve">bigmove.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -534,7 +534,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -549,7 +549,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.ojousama[3]</t>
+          <t xml:space="preserve">bigmove.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -566,7 +566,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -581,7 +581,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.ojousama[1]</t>
+          <t xml:space="preserve">climax.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -598,7 +598,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -613,7 +613,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.ojousama[2]</t>
+          <t xml:space="preserve">climax.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -630,7 +630,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -645,7 +645,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -662,7 +662,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -677,7 +677,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -694,7 +694,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -726,7 +726,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -741,7 +741,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal.ojousama[1]</t>
+          <t xml:space="preserve">badWinner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -758,7 +758,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -773,7 +773,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.ojousama[1]</t>
+          <t xml:space="preserve">goodWinner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -790,7 +790,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.ojousama[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -805,7 +805,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.ojousama[2]</t>
+          <t xml:space="preserve">goodWinner.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -822,7 +822,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -837,7 +837,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -854,7 +854,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -869,7 +869,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -886,7 +886,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -901,7 +901,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -918,7 +918,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.ojousama[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -933,7 +933,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.ojousama[2]</t>
+          <t xml:space="preserve">loser.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -950,7 +950,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -965,7 +965,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -982,7 +982,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.ojousama[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -997,7 +997,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.ojousama[2]</t>
+          <t xml:space="preserve">winner.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1014,7 +1014,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.ojousama[1]</t>
+          <t xml:space="preserve">competition_won.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1046,7 +1046,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.ojousama[2]</t>
+          <t xml:space="preserve">competition_won.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1078,7 +1078,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.ojousama[1]</t>
+          <t xml:space="preserve">direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1110,7 +1110,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.ojousama[2]</t>
+          <t xml:space="preserve">direct.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1142,7 +1142,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.ojousama[1]</t>
+          <t xml:space="preserve">fa_signing.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1174,7 +1174,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.ojousama[2]</t>
+          <t xml:space="preserve">fa_signing.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1206,7 +1206,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.ojousama.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.normal.hit[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama.hit[1]</t>
+          <t xml:space="preserve">ojousama.normal.hit[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1238,7 +1238,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.ojousama.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.normal.hit[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama.hit[2]</t>
+          <t xml:space="preserve">ojousama.normal.hit[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1270,7 +1270,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.ojousama.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.normal.win[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama.win[1]</t>
+          <t xml:space="preserve">ojousama.normal.win[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1302,7 +1302,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.ojousama.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.normal.win[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama.win[2]</t>
+          <t xml:space="preserve">ojousama.normal.win[2]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1334,7 +1334,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1398,7 +1398,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1430,7 +1430,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1462,7 +1462,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1494,7 +1494,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1590,7 +1590,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1622,7 +1622,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1782,7 +1782,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1814,7 +1814,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1846,7 +1846,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1878,7 +1878,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1910,7 +1910,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1942,7 +1942,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2006,7 +2006,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2038,7 +2038,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2070,7 +2070,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2102,7 +2102,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2134,7 +2134,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.ojousama[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.ojousama[2]</t>
+          <t xml:space="preserve">attacker.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2166,7 +2166,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2198,7 +2198,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.ojousama[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.ojousama[2]</t>
+          <t xml:space="preserve">defender.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2230,7 +2230,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.ojousama[1]</t>
+          <t xml:space="preserve">fateAttacker.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2262,7 +2262,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.ojousama[1]</t>
+          <t xml:space="preserve">fateDefender.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2294,7 +2294,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2326,7 +2326,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2358,7 +2358,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.ojousama[1]</t>
+          <t xml:space="preserve">fateLoser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2390,7 +2390,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.ojousama[1]</t>
+          <t xml:space="preserve">fateWinner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2422,7 +2422,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2454,7 +2454,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2486,7 +2486,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2518,7 +2518,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2550,7 +2550,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.ojousama[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.ojousama[1]</t>
+          <t xml:space="preserve">awakening.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -3350,7 +3350,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.ojousama[1]</t>
+          <t xml:space="preserve">accepted.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3382,7 +3382,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.ojousama[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.ojousama[2]</t>
+          <t xml:space="preserve">accepted.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3414,7 +3414,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.ojousama[1]</t>
+          <t xml:space="preserve">defended.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.ojousama[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.ojousama[2]</t>
+          <t xml:space="preserve">defended.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3510,7 +3510,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.ojousama[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.ojousama[2]</t>
+          <t xml:space="preserve">defense_failed.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3542,7 +3542,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.ojousama[1]</t>
+          <t xml:space="preserve">default.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">former_champ.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3606,7 +3606,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3638,7 +3638,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3670,7 +3670,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_former_champ.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3702,7 +3702,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3734,7 +3734,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_no_title.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3766,7 +3766,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_terminal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3798,7 +3798,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.ojousama[1]</t>
+          <t xml:space="preserve">accept_winless.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3830,7 +3830,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_champ.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3862,7 +3862,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_distrust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3894,7 +3894,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_fighting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3926,7 +3926,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">refuse_heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3958,7 +3958,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">A1_champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3990,7 +3990,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4022,7 +4022,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4054,7 +4054,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4086,7 +4086,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4118,7 +4118,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4150,7 +4150,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4182,7 +4182,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_champion_injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4214,7 +4214,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4246,7 +4246,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4278,7 +4278,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4310,7 +4310,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4342,7 +4342,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4374,7 +4374,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.ojousama[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4406,7 +4406,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4438,7 +4438,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.ojousama[2]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4470,7 +4470,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.ojousama[1]</t>
+          <t xml:space="preserve">transfer_listen.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4502,7 +4502,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.ojousama[1]</t>
+          <t xml:space="preserve">transfer_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4534,7 +4534,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.ojousama[1]</t>
+          <t xml:space="preserve">transfer_release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4566,7 +4566,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4598,7 +4598,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_success.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4630,7 +4630,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.normal.ojousama[1]</t>
+          <t xml:space="preserve">blocked.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4663,7 +4663,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.normal.ojousama[1]</t>
+          <t xml:space="preserve">fail.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4695,7 +4695,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.ojousama[1]</t>
+          <t xml:space="preserve">start.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4728,7 +4728,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.normal.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.normal.ojousama[1]</t>
+          <t xml:space="preserve">success.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4761,7 +4761,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4793,7 +4793,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4825,7 +4825,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4857,7 +4857,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.ojousama[1]</t>
+          <t xml:space="preserve">cap_reached.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4889,7 +4889,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.ojousama[1]</t>
+          <t xml:space="preserve">ovr_elite.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4921,7 +4921,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.ojousama[1]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4953,7 +4953,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.ojousama[1]</t>
+          <t xml:space="preserve">ovr_legend.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4985,7 +4985,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.ojousama[1]</t>
+          <t xml:space="preserve">pop_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5017,7 +5017,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.ojousama[1]</t>
+          <t xml:space="preserve">pop_star.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5049,7 +5049,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5081,7 +5081,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5113,7 +5113,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5145,7 +5145,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.ojousama[1]</t>
+          <t xml:space="preserve">defeat.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5177,7 +5177,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5209,7 +5209,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.ojousama[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5241,7 +5241,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.ojousama[1]</t>
+          <t xml:space="preserve">penalty_end.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5273,7 +5273,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5305,7 +5305,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5337,7 +5337,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.ojousama[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5369,7 +5369,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.ojousama[1]</t>
+          <t xml:space="preserve">mediaAward.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5401,7 +5401,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.ojousama[1]</t>
+          <t xml:space="preserve">mvp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5433,7 +5433,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.ojousama[1]</t>
+          <t xml:space="preserve">rookie.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5465,7 +5465,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5497,7 +5497,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5529,7 +5529,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5561,7 +5561,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5593,7 +5593,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5625,7 +5625,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5657,7 +5657,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.ojousama[1]</t>
+          <t xml:space="preserve">N1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5689,7 +5689,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.ojousama[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.ojousama[2]</t>
+          <t xml:space="preserve">N1.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5721,7 +5721,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.ojousama[1]</t>
+          <t xml:space="preserve">N2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5753,7 +5753,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.ojousama[1]</t>
+          <t xml:space="preserve">N3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5785,7 +5785,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.ojousama[1]</t>
+          <t xml:space="preserve">N4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5817,7 +5817,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.ojousama[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5849,7 +5849,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.ojousama[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5881,7 +5881,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal.ojousama[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5913,7 +5913,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.ojousama[1]</t>
+          <t xml:space="preserve">bonus_insult.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5945,7 +5945,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.ojousama[1]</t>
+          <t xml:space="preserve">bonus.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5977,7 +5977,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.ojousama[1]</t>
+          <t xml:space="preserve">camp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6009,7 +6009,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.ojousama[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6041,7 +6041,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.ojousama[1]</t>
+          <t xml:space="preserve">encourage.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6073,7 +6073,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.ojousama[1]</t>
+          <t xml:space="preserve">media.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6105,7 +6105,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.ojousama[1]</t>
+          <t xml:space="preserve">party.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6137,7 +6137,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.ojousama[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6169,7 +6169,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.ojousama[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6201,7 +6201,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.ojousama[1]</t>
+          <t xml:space="preserve">trainer.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6233,7 +6233,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.ojousama[1]</t>
+          <t xml:space="preserve">E1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6265,7 +6265,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.normal.ojousama[1]</t>
+          <t xml:space="preserve">E4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6297,7 +6297,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.ojousama[1]</t>
+          <t xml:space="preserve">E6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6329,7 +6329,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6361,7 +6361,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.ojousama[1]</t>
+          <t xml:space="preserve">S_grumble.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6393,7 +6393,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.ojousama[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6425,7 +6425,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.ojousama[1]</t>
+          <t xml:space="preserve">S1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6457,7 +6457,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.ojousama[1]</t>
+          <t xml:space="preserve">S2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6489,7 +6489,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.ojousama[1]</t>
+          <t xml:space="preserve">S3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6521,7 +6521,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.ojousama[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6553,7 +6553,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.normal.ojousama[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6585,7 +6585,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.ojousama[1]</t>
+          <t xml:space="preserve">S5.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6617,7 +6617,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.ojousama[1]</t>
+          <t xml:space="preserve">S6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6649,7 +6649,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.ojousama[1]</t>
+          <t xml:space="preserve">B1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6681,7 +6681,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6713,7 +6713,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6745,7 +6745,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6777,7 +6777,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6809,7 +6809,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_fan.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6841,7 +6841,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6873,7 +6873,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6905,7 +6905,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6937,7 +6937,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.ojousama[1]</t>
+          <t xml:space="preserve">B4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6969,7 +6969,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7001,7 +7001,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7033,7 +7033,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7065,7 +7065,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7097,7 +7097,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7129,7 +7129,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7161,7 +7161,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7193,7 +7193,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7225,7 +7225,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7257,7 +7257,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.ojousama[2]</t>
+          <t xml:space="preserve">draftJoin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7289,7 +7289,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7321,7 +7321,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7353,7 +7353,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.ojousama[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7385,7 +7385,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.ojousama[1]</t>
+          <t xml:space="preserve">injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7417,7 +7417,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.ojousama[2]</t>
+          <t xml:space="preserve">injury.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7449,7 +7449,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.ojousama[1]</t>
+          <t xml:space="preserve">release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7481,7 +7481,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.ojousama[2]</t>
+          <t xml:space="preserve">release.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7513,7 +7513,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7545,7 +7545,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal.ojousama[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7577,7 +7577,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7609,7 +7609,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7641,7 +7641,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7673,7 +7673,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7705,7 +7705,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7737,7 +7737,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7769,7 +7769,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7801,7 +7801,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7833,7 +7833,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7865,7 +7865,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7897,7 +7897,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8281,7 +8281,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8313,7 +8313,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8345,7 +8345,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.loss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8377,7 +8377,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-01.win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8409,7 +8409,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8441,7 +8441,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8473,7 +8473,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8505,7 +8505,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8537,7 +8537,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8569,7 +8569,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8601,7 +8601,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8633,7 +8633,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8665,7 +8665,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8697,7 +8697,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8729,7 +8729,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.ojousama[1]</t>
+          <t xml:space="preserve">GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8761,7 +8761,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8793,7 +8793,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8825,7 +8825,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8857,7 +8857,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8889,7 +8889,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8921,7 +8921,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.ojousama[1]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8953,7 +8953,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.ojousama[2]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8985,7 +8985,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9017,7 +9017,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9049,7 +9049,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.ojousama[1]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9081,7 +9081,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.ojousama[2]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9113,7 +9113,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.ojousama[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9145,7 +9145,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.ojousama[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9177,7 +9177,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9209,7 +9209,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.ojousama[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9241,7 +9241,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.ojousama[1]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9273,7 +9273,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.ojousama[2]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9305,7 +9305,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9337,7 +9337,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9369,7 +9369,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.ojousama[1]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9401,7 +9401,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.ojousama[2]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9433,7 +9433,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9465,7 +9465,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.ojousama[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9497,7 +9497,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9529,7 +9529,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9561,7 +9561,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.ojousama[1]</t>
+          <t xml:space="preserve">summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9593,7 +9593,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.ojousama[2]</t>
+          <t xml:space="preserve">summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9625,7 +9625,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9657,7 +9657,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9689,7 +9689,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9721,7 +9721,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.ojousama[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9753,7 +9753,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.ojousama[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9785,7 +9785,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.ojousama[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9817,7 +9817,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.ojousama[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9849,7 +9849,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.ojousama[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.ojousama[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9881,7 +9881,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.ojousama[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.ojousama[2]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9913,7 +9913,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.ojousama[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.ojousama[1]</t>
+          <t xml:space="preserve">result_win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9945,7 +9945,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.ojousama[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.ojousama[2]</t>
+          <t xml:space="preserve">result_win.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9977,7 +9977,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10009,7 +10009,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10041,7 +10041,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.ojousama[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10073,7 +10073,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal.ojousama[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.ojousama[1]</t>
+          <t xml:space="preserve">fighter.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10105,7 +10105,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10137,7 +10137,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H310"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ…お見事でしたでしょう？</t>
+          <t xml:space="preserve">ふぅ……今日は、思い描いた通りに動けたわね</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わって無いのでしょうね。あちらの目はまだ死んでいないようですし。</t>
+          <t xml:space="preserve">まだ終わっていないのでしょうね。あちらの目はまだ死んでいないようですし。</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…一つ答えがたわね。…でも、終わりではないわよ</t>
+          <t xml:space="preserve">ようやく…一つ答えが出たわね。…でも、終わりではないわよ</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご覧になって？ 格上ですって……もう言えないわね</t>
+          <t xml:space="preserve">格上……その言葉に、もう意味はないわね。積み上げてきたものが上回った、それだけですもの</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちましたわ! ……お骨折り、ありがとうございました。</t>
+          <t xml:space="preserve">勝ちましたわ！ ……お骨折り、ありがとうございました。</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご報告です。勝ってまいりました!</t>
+          <t xml:space="preserve">ご報告です。勝ってまいりました！</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのですね…感慨深いですわ</t>
+          <t xml:space="preserve">ここまで来られたのですね…感慨深いですわ</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何のために…闘っているのかしら、わたし</t>
+          <t xml:space="preserve">何のために…闘っているのかしら、私</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…やれるわ。やって見せる</t>
+          <t xml:space="preserve">まだ…やれるわ。やってみせる</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…戻ってこれましたわ</t>
+          <t xml:space="preserve">ようやく…戻ってこられましたわ</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治りったのに…動けない……なぜ？</t>
+          <t xml:space="preserve">体は治ったのに…動けない……なぜ？</t>
         </is>
       </c>
     </row>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は癒えましたのに…気力が戻ないわね</t>
+          <t xml:space="preserve">怪我は癒えましたのに…気力が戻らないわね</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あのような激闘、生涯忘れませんわ。対戦してくれたお相手に、心より敬意を</t>
+          <t xml:space="preserve">我が団体の誇りを、この対抗戦で示せましたわ。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5330,14 +5330,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この王座をお預かりしている限り、最高の試合をお約束いたします</t>
+          <t xml:space="preserve">あのような激闘、生涯忘れませんわ。対戦してくれたお相手に、心より敬意を</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.normal[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5362,14 +5362,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">華やかな舞台から降りる日が来たということ。…でも、後悔はございません</t>
+          <t xml:space="preserve">この王座をお預かりしている限り、最高の試合をお約束いたします</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.ojousama.normal[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">光栄でございます。また精進いたします</t>
+          <t xml:space="preserve">華やかな舞台から降りる日が来たということ。…でも、後悔はございません</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.normal[1]</t>
+          <t xml:space="preserve">mediaAward.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年を通して成長できましたこと、皆さまのおかげです</t>
+          <t xml:space="preserve">光栄でございます。また精進いたします</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.normal[1]</t>
+          <t xml:space="preserve">mvp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさかわたくしがこのような栄誉に…。先輩方の背中、しかと見ておりました</t>
+          <t xml:space="preserve">一年を通して成長できましたこと、皆さまのおかげです</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">rookie.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5490,14 +5490,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングに立てますこと、身に余る光栄ですわ</t>
+          <t xml:space="preserve">まさかわたくしがこのような栄誉に…。先輩方の背中、しかと見ておりました</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5522,14 +5522,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このような大舞台、夢にまで見ましたのよ</t>
+          <t xml:space="preserve">この栄冠は、わたくしたち二人の信頼が結んだものですわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[3]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日を、生涯忘れませんわ</t>
+          <t xml:space="preserve">ドームのリングに立てますこと、身に余る光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員御礼、まさに奇跡のような景色ですわ…</t>
+          <t xml:space="preserve">このような大舞台、夢にまで見ましたのよ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5618,14 +5618,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の熱気、今も胸に残っておりますの</t>
+          <t xml:space="preserve">今日という日を、生涯忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[3]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5650,14 +5650,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この日のこと、生涯の誇りとしますわ</t>
+          <t xml:space="preserve">満員御礼、まさに奇跡のような景色ですわ…</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5667,29 +5667,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">稽古が楽しくなってまいりました</t>
+          <t xml:space="preserve">お客様の熱気、今も胸に残っておりますの</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5699,29 +5699,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しずつ、体が応えてくれるようになってきたわね</t>
+          <t xml:space="preserve">この日のこと、生涯の誇りとしますわ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.ojousama.normal[1]</t>
+          <t xml:space="preserve">N1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い仲間に恵まれたわね</t>
+          <t xml:space="preserve">稽古が楽しくなってまいりました</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.ojousama.normal[1]</t>
+          <t xml:space="preserve">N1.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5778,14 +5778,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少々疲れが出たようで…次までには整えます</t>
+          <t xml:space="preserve">少しずつ、体が応えてくれるようになってきたわね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.ojousama.normal[1]</t>
+          <t xml:space="preserve">N2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様からこれほどの声援をいただけるのは、光栄です</t>
+          <t xml:space="preserve">良い仲間に恵まれたわね</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.ojousama.normal[1]</t>
+          <t xml:space="preserve">N3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5842,14 +5842,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう結構ですわ</t>
+          <t xml:space="preserve">少々疲れが出たようで…次までには整えます</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.ojousama.normal[1]</t>
+          <t xml:space="preserve">N4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、考え事がございまして</t>
+          <t xml:space="preserve">皆様からこれほどの声援をいただけるのは、光栄です</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.ojousama.normal[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5906,14 +5906,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お金のことで文句を言うつもりはないけれど</t>
+          <t xml:space="preserve">…もう結構ですわ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5923,29 +5923,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.ojousama.normal[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ。……わたくし、この程度に見られていましたのね</t>
+          <t xml:space="preserve">…少し、考え事がございまして</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5955,29 +5955,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.ojousama.normal[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、ありがとうございます。大切に使わせていただきます</t>
+          <t xml:space="preserve">…お金のことで文句を言うつもりはないけれど</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.ojousama.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿ですの？ 精一杯取り組みますわ</t>
+          <t xml:space="preserve">まあ。……わたくし、この程度に見られていましたのね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.ojousama.normal[1]</t>
+          <t xml:space="preserve">bonus.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6034,14 +6034,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見守ってくださったんですのね…その気持ちに、お応えしなくては</t>
+          <t xml:space="preserve">まあ、ありがとうございます。大切に使わせていただきます</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.ojousama.normal[1]</t>
+          <t xml:space="preserve">camp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6066,14 +6066,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。もう少し、頑張ってみます</t>
+          <t xml:space="preserve">合宿ですの？ 精一杯取り組みますわ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.ojousama.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6098,14 +6098,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアのお仕事ですの？ 精一杯務めます</t>
+          <t xml:space="preserve">ずっと見守ってくださったんですのね…その気持ちに、お応えしなくては</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.ojousama.normal[1]</t>
+          <t xml:space="preserve">encourage.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しいお時間でしたわ。それでは、ごきげんよう</t>
+          <t xml:space="preserve">…ありがとうございます。もう少し、頑張ってみます</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.ojousama.normal[1]</t>
+          <t xml:space="preserve">media.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。リフレッシュして戻って参ります</t>
+          <t xml:space="preserve">メディアのお仕事ですの？ 精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.ojousama.normal[1]</t>
+          <t xml:space="preserve">party.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6194,14 +6194,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…そこまでしてくださるなんて。早く戻りますわ</t>
+          <t xml:space="preserve">楽しいお時間でしたわ。それでは、ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.ojousama.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6226,14 +6226,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯、学ばせていただきます</t>
+          <t xml:space="preserve">ありがとうございます。リフレッシュして戻って参ります</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.normal[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアのお話ですの？ ぜひお受けしたいですわ</t>
+          <t xml:space="preserve">まあ…そこまでしてくださるなんて。早く戻りますわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.ojousama.normal[1]</t>
+          <t xml:space="preserve">trainer.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しいスカウトのお話が、届いているそうです</t>
+          <t xml:space="preserve">精一杯、学ばせていただきます</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.ojousama.normal[1]</t>
+          <t xml:space="preserve">E1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6322,14 +6322,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からお話がございましたの…</t>
+          <t xml:space="preserve">メディアのお話ですの？ ぜひお受けしたいですわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.normal[1]</t>
+          <t xml:space="preserve">E4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6354,14 +6354,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はお稽古をお休みさせていただきますわ…理由は…ご想像にお任せしますわ</t>
+          <t xml:space="preserve">新しいスカウトのお話が、届いているそうです</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.ojousama.normal[1]</t>
+          <t xml:space="preserve">E6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（控室で「あの方の采配、少しおかしくなくて？」と囁いている）</t>
+          <t xml:space="preserve">他の団体からお話がございましたの…</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.ojousama.normal[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6418,14 +6418,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「窮屈な場所からは、いつでも出ていけますの」と投稿）</t>
+          <t xml:space="preserve">今日はお稽古をお休みさせていただきますわ…理由は…ご想像にお任せしますわ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.ojousama.normal[1]</t>
+          <t xml:space="preserve">S_grumble.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6450,14 +6450,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座への挑戦をお許しいただけませんこと？</t>
+          <t xml:space="preserve">（控室で「あの方の采配、少しおかしくなくて？」と囁いている）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.ojousama.normal[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方との決着を、お許しいただけませんか？</t>
+          <t xml:space="preserve">（SNSに「窮屈な場所からは、いつでも出ていけますの」と投稿）</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.ojousama.normal[1]</t>
+          <t xml:space="preserve">S1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお休みをいただけますかしら…</t>
+          <t xml:space="preserve">王座への挑戦をお許しいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.ojousama.normal[1]</t>
+          <t xml:space="preserve">S2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは困ります！お話し合いをさせてくださいまし</t>
+          <t xml:space="preserve">あの方との決着を、お許しいただけませんか？</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.ojousama.normal[1]</t>
+          <t xml:space="preserve">S3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6578,14 +6578,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…申し上げたいことは、ございます。けれど、口にはできません）</t>
+          <t xml:space="preserve">少しお休みをいただけますかしら…</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.ojousama.normal[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6610,14 +6610,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓の時間をいただけませんこと？</t>
+          <t xml:space="preserve">このままでは困ります！お話し合いをさせてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.ojousama.normal[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩のお世話は、私にお任せください</t>
+          <t xml:space="preserve">（…申し上げたいことは、ございます。けれど、口にはできません）</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.ojousama.normal[1]</t>
+          <t xml:space="preserve">S5.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6674,14 +6674,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお時間をいただくことになりそうですわ…</t>
+          <t xml:space="preserve">特訓の時間をいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.ojousama.normal[1]</t>
+          <t xml:space="preserve">S6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6706,14 +6706,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…もう限界ですわ</t>
+          <t xml:space="preserve">後輩のお世話は、私にお任せください</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.ojousama.normal[1]</t>
+          <t xml:space="preserve">B1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちらにも非がおありでしょうに…</t>
+          <t xml:space="preserve">少しお時間をいただくことになりそうですわ…</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.ojousama.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6770,14 +6770,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、コラボのお話ですの。嬉しい限りですわ</t>
+          <t xml:space="preserve">あの方とは…もう限界ですわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.ojousama.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6802,14 +6802,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMですか。しっかりお役目を果たしますわ</t>
+          <t xml:space="preserve">あちらにも非がおありでしょうに…</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6834,14 +6834,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に直接お礼を申し上げる機会ですわね</t>
+          <t xml:space="preserve">まあ、コラボのお話ですの。嬉しい限りですわ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6866,14 +6866,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイですか。精一杯美しく歩いてみせますわ</t>
+          <t xml:space="preserve">CMですか。しっかりお役目を果たしますわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_fan.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6898,14 +6898,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">撮影ですか。美しく仕上げていただけるよう努めますわ</t>
+          <t xml:space="preserve">ファンの方々に直接お礼を申し上げる機会ですわね</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ番組ですか。品よくふるまえるよう努めますわ</t>
+          <t xml:space="preserve">ランウェイですか。精一杯美しく歩いてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6962,14 +6962,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材ですか？ 精一杯務めさせていただきます</t>
+          <t xml:space="preserve">撮影ですか。美しく仕上げていただけるよう努めますわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6979,29 +6979,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
+          <t xml:space="preserve">バラエティ番組ですか。品よくふるまえるよう努めますわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7011,29 +7011,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">B4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
+          <t xml:space="preserve">取材ですか？ 精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7058,14 +7058,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
+          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
@@ -7090,14 +7090,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
+          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7122,14 +7122,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
@@ -7154,14 +7154,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7186,14 +7186,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
+          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7235,12 +7235,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7250,14 +7250,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
+          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.normal[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7282,14 +7282,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
+          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7314,14 +7314,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">行くあての無いわたくしを招いてくださって。恩は必ずお返しします</t>
+          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.normal[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7346,14 +7346,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.normal[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
+          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.normal[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7410,14 +7410,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.normal[2]</t>
+          <t xml:space="preserve">faWelcome.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.normal[1]</t>
+          <t xml:space="preserve">injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
+          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.normal[2]</t>
+          <t xml:space="preserve">injury.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
+          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
+          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">release.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7570,14 +7570,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを見つけたご慧眼、称えて差し上げます</t>
+          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7602,14 +7602,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7634,14 +7634,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
+          <t xml:space="preserve">見つけていただいたからには、お応えするわ。……期待を裏切るつもりはないもの</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7666,14 +7666,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
+          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7698,14 +7698,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンですわ…！夢のようですわね…！</t>
+          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
+          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">titleWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7762,14 +7762,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
+          <t xml:space="preserve">……ベルトが、こんなに重いなんて。……確かに、この手で掴んだのね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
+          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7826,14 +7826,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
+          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
@@ -7858,14 +7858,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
@@ -7890,14 +7890,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
+          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
@@ -7922,14 +7922,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンですわ…！夢のようですわね…！</t>
+          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7939,29 +7939,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう以前のようには戻れませんわ</t>
+          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7971,29 +7971,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し距離ができたように感じますわ</t>
+          <t xml:space="preserve">……ベルトが、こんなに重いなんて。……確かに、この手で掴んだのね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8018,14 +8018,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不思議と波長が合いますの。心地よい距離感ですわ</t>
+          <t xml:space="preserve">もう以前のようには戻れませんわ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8050,14 +8050,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">かけがえのない方ですわ。何物にも代えられません</t>
+          <t xml:space="preserve">少し距離ができたように感じますわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう過去のことですわ</t>
+          <t xml:space="preserve">不思議と波長が合いますの。心地よい距離感ですわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8114,14 +8114,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくありませんわ…こんな気持ちは初めて</t>
+          <t xml:space="preserve">かけがえのない方ですわ。何物にも代えられません</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8146,14 +8146,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何としてでも超えてみせますわ</t>
+          <t xml:space="preserve">もう過去のことですわ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8178,14 +8178,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの宿命ですわ…それ以外に言葉がない</t>
+          <t xml:space="preserve">負けたくありませんわ…こんな気持ちは初めて</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8210,14 +8210,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここがわたくしの居場所ですわ。誇りに思います</t>
+          <t xml:space="preserve">何としてでも超えてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8242,14 +8242,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このような扱いを受ける覚えはございませんわ</t>
+          <t xml:space="preserve">わたくしの宿命ですわ…それ以外に言葉がない</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.ojousama[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8274,14 +8274,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の運営方針に…疑問を感じますわ</t>
+          <t xml:space="preserve">ここがわたくしの居場所ですわ。誇りに思います</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8306,14 +8306,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">敗北は悔しいですけど…素晴らしい試合でした</t>
+          <t xml:space="preserve">このような扱いを受ける覚えはございませんわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8338,14 +8338,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素晴らしい勝利ですわ。この舞台に相応しい試合でした</t>
+          <t xml:space="preserve">この団体の運営方針に…疑問を感じますわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8370,14 +8370,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この敗北…受け入れがたいわね</t>
+          <t xml:space="preserve">敗北は悔しいですけど…素晴らしい試合でした</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8402,14 +8402,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利。当然の結果ですけどね</t>
+          <t xml:space="preserve">素晴らしい勝利ですわ。この舞台に相応しい試合でした</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8434,14 +8434,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
+          <t xml:space="preserve">この敗北…受け入れがたいわね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8466,14 +8466,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
+          <t xml:space="preserve">勝てたわ。……積み上げたものが、出ただけね</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8498,14 +8498,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待遇には満足しております</t>
+          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8530,14 +8530,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
+          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動向が…気になります</t>
+          <t xml:space="preserve">待遇には満足しております</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8594,14 +8594,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
+          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8626,14 +8626,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調が…あまり芳しくありません</t>
+          <t xml:space="preserve">動向が…気になります</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
+          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8690,14 +8690,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
+          <t xml:space="preserve">体調が…あまり芳しくありません</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8722,14 +8722,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
+          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8754,14 +8754,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
+          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8786,14 +8786,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
+          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8803,29 +8803,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8835,29 +8835,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
+          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8882,14 +8882,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
+          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8914,14 +8914,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
+          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.normal[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お見送りしましたわ。…息は乱れていますけれど、退きませんの。次はどなた?</t>
+          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.normal[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8978,14 +8978,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだこのリングに立っていますのよ。次の方、早くいらして</t>
+          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9010,14 +9010,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはなりませんの</t>
+          <t xml:space="preserve">一人、倒したわ。…少し息は乱れているけれど。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9042,14 +9042,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
+          <t xml:space="preserve">待ちきれませんわね。次の方、早くいらして</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.normal[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりませんの</t>
+          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはまいりません</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.normal[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞だけでは、わたくし、満足できませんわ。次は三人で勝ちますの</t>
+          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.normal[1]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お身体はもう悲鳴を上げていますわ。ですが……このリングを明け渡す理由にはなりませんの</t>
+          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりません</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.normal[2]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
+          <t xml:space="preserve">この賞だけでは、わたくし、満足できません。次は三人で勝ちますわ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9202,14 +9202,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
+          <t xml:space="preserve">身体はもう悲鳴を上げています。ですが……このリングを明け渡す理由にはなりませんの</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9234,14 +9234,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
+          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.normal[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
+          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.normal[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9298,14 +9298,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
+          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9330,14 +9330,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
+          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次もこの調子で参ります</t>
+          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
+          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9426,14 +9426,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実りある大会でした</t>
+          <t xml:space="preserve">次もこの調子で参ります</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9458,14 +9458,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝。全てを出し切ります</t>
+          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
+          <t xml:space="preserve">実りある大会でした</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
+          <t xml:space="preserve">決勝。全てを出し切ります</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
+          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.normal[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9586,14 +9586,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
+          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.normal[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
+          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9650,14 +9650,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
+          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
+          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9714,14 +9714,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
+          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
@@ -9746,14 +9746,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、こちらの団体さん？ 随分とかわいらしい興行をなさっていますわね</t>
+          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
@@ -9778,14 +9778,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
+          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
+          <t xml:space="preserve">そちらの興行、拝見したわ。……少し、もの足りないわね。私が出れば、変わるはずですもの</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
@@ -9842,14 +9842,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
+          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9874,14 +9874,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
+          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9906,14 +9906,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
+          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.normal[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9938,14 +9938,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
+          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.normal[2]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9970,14 +9970,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
+          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">result_win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10002,14 +10002,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
+          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">result_win.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10034,14 +10034,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
+          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[3]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10066,14 +10066,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
+          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10083,29 +10083,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れたのね…感無量だわ</t>
+          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10115,59 +10115,123 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">行くあての無いわたくしを招いてくださって。恩は必ずお返しします</t>
+          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られたのね…感無量だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr" s="2">
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr" s="12">
+      <c r="D310" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr" s="2">
+      <c r="E310" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">わたくしを見つけたご慧眼、称えて差し上げます</t>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見つけていただいたからには、お応えするわ。……期待を裏切るつもりはないもの</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H308"/>
+  <autoFilter ref="A1:H310"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H310"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4246,7 +4246,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.ojousama.normal[1]</t>
+          <t xml:space="preserve">decline_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。より一層、精進いたしますわね。</t>
+          <t xml:space="preserve">……それで結構です。足りないところは、練習で埋めます。……それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.ojousama.normal[1]</t>
+          <t xml:space="preserve">decline_hold.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そのお気持ちだけでも、嬉しいわ。</t>
+          <t xml:space="preserve">……据え置き……？ ……その分は、来季の数字で返します。必ず</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.ojousama.normal[1]</t>
+          <t xml:space="preserve">decline_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……左様ですか。承知いたしました。</t>
+          <t xml:space="preserve">……ええ。自分の調子は、自分がいちばん分かっていますもの。……驚きません</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.ojousama.normal[1]</t>
+          <t xml:space="preserve">decline_strict.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お時間よろしいかしら。{tenure}待遇について、ご相談させてください。{record}</t>
+          <t xml:space="preserve">……そうですか。……よくわかりました。ここは、そういう場所なのですね</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.ojousama.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうですか。承知いたしました……。</t>
+          <t xml:space="preserve">……ええ、それでいい。……見合う額のほうが、迷わずに済みます</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、要点だけ申し上げます。辞めます。もう決めましたの。</t>
+          <t xml:space="preserve">……変えない、と。……では、その額に見合うところまで戻すだけですね</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.normal[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。ですが、もうここに留まることはできません。</t>
+          <t xml:space="preserve">社長。……全盛は過ぎました。相応の額に、書き直してくださいませ</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.ojousama.normal[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4495,14 +4495,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お耳を傾けてくださるのね。{record}新たな場所で己を試したいのです。</t>
+          <t xml:space="preserve">ありがとうございますわ。より一層、精進いたしますわね。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.ojousama.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}お伝えしづらいのですが…退団を考えておりますの。</t>
+          <t xml:space="preserve">……そのお気持ちだけでも、嬉しいわ。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.ojousama.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4559,14 +4559,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。{tenure_farewell}{rivalry}ごきげんよう。</t>
+          <t xml:space="preserve">……左様ですか。承知いたしました。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.ojousama.normal[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お気持ちは嬉しいのですが…もう、決めました。</t>
+          <t xml:space="preserve">社長、お時間よろしいかしら。{tenure}待遇について、ご相談させてください。{record}</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.ojousama.normal[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4623,401 +4623,401 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまでおっしゃるなら。もう少しお付き合いいたします。</t>
+          <t xml:space="preserve">……そうですか。承知いたしました……。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、要点だけ申し上げます。辞めます。もう決めましたの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.normal[2]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.ojousama.normal[2]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お世話になりました。ですが、もうここに留まることはできません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お耳を傾けてくださるのね。{record}新たな場所で己を試したいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}お伝えしづらいのですが…退団を考えておりますの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしました。{tenure_farewell}{rivalry}ごきげんよう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お気持ちは嬉しいのですが…もう、決めました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そこまでおっしゃるなら。もう少しお付き合いいたします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr" s="12">
+      <c r="D143" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr" s="2">
+      <c r="E143" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr" s="3">
+      <c r="F143" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">大変恐縮ですが、そのようなお話は伺えませんわ。
 今の団体への思いは揺らぎませんの</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="40" customHeight="1">
-      <c r="A137" t="inlineStr" s="15">
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr" s="2">
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr" s="12">
+      <c r="D144" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr" s="2">
+      <c r="E144" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr" s="3">
+      <c r="F144" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">申し訳ありませんが、今回はご遠慮しますわ</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="40" customHeight="1">
-      <c r="A138" t="inlineStr" s="15">
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr" s="2">
+      <c r="B145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr" s="12">
+      <c r="D145" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr" s="2">
+      <c r="E145" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr" s="3">
+      <c r="F145" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしをお誘いですの？
 …条件次第ですわね</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="40" customHeight="1">
-      <c r="A139" t="inlineStr" s="15">
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr" s="2">
+      <c r="B146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr" s="12">
+      <c r="D146" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr" s="2">
+      <c r="E146" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr" s="3">
+      <c r="F146" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…承知しましたわ。
 実力で居場所を作ってみせます</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="40" customHeight="1">
-      <c r="A140" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">率直に申し上げます。このままでは、わたくしたちは朽ちますわ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="40" customHeight="1">
-      <c r="A141" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">何かが変わった気がいたします…壁を越えたのね</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="40" customHeight="1">
-      <c r="A142" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">（…体が軽いわ。何かが変わったかしら——）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="40" customHeight="1">
-      <c r="A143" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここが限界…でも、ここまで来られたことに感謝ですわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="40" customHeight="1">
-      <c r="A144" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来られたのですね…感慨深いですわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="40" customHeight="1">
-      <c r="A145" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">確かに成長を感じますわ。…まだまだですけれど</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="40" customHeight="1">
-      <c r="A146" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.ojousama.normal[1]</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">この領域に立てたのは…光栄ですわ</t>
-        </is>
-      </c>
-    </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.ojousama.normal[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしのことを知ってくださる方が増えましたわ</t>
+          <t xml:space="preserve">率直に申し上げます。このままでは、わたくしたちは朽ちますわ。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.normal[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これだけの方に応援いただけるなんて…身が引き締まりますわ</t>
+          <t xml:space="preserve">何かが変わった気がいたします…壁を越えたのね</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
@@ -5074,14 +5074,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何のために…闘っているのかしら、私</t>
+          <t xml:space="preserve">（…体が軽いわ。何かが変わったかしら——）</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">cap_reached.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5106,14 +5106,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ…やれるわ。やってみせる</t>
+          <t xml:space="preserve">ここが限界…でも、ここまで来られたことに感謝ですわ</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">ovr_elite.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5138,14 +5138,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく…戻ってこられましたわ</t>
+          <t xml:space="preserve">ここまで来られたのですね…感慨深いですわ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.ojousama.normal[1]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5170,14 +5170,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの敗北から…何かがおかしい気がする</t>
+          <t xml:space="preserve">確かに成長を感じますわ。…まだまだですけれど</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.ojousama.normal[1]</t>
+          <t xml:space="preserve">ovr_legend.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5202,14 +5202,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治ったのに…動けない……なぜ？</t>
+          <t xml:space="preserve">この領域に立てたのは…光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.ojousama.normal[1]</t>
+          <t xml:space="preserve">pop_growth.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに戻れたというのに…怖いわ</t>
+          <t xml:space="preserve">わたくしのことを知ってくださる方が増えましたわ</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.ojousama.normal[1]</t>
+          <t xml:space="preserve">pop_star.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5266,14 +5266,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は癒えましたのに…気力が戻らないわね</t>
+          <t xml:space="preserve">これだけの方に応援いただけるなんて…身が引き締まりますわ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5283,29 +5283,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">我が団体の誇りを、この対抗戦で示せましたわ。</t>
+          <t xml:space="preserve">何のために…闘っているのかしら、私</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5315,29 +5315,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あのような激闘、生涯忘れませんわ。対戦してくれたお相手に、心より敬意を</t>
+          <t xml:space="preserve">まだ…やれるわ。やってみせる</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5347,29 +5347,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この王座をお預かりしている限り、最高の試合をお約束いたします</t>
+          <t xml:space="preserve">ようやく…戻ってこられましたわ</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5379,29 +5379,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.normal[1]</t>
+          <t xml:space="preserve">defeat.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">華やかな舞台から降りる日が来たということ。…でも、後悔はございません</t>
+          <t xml:space="preserve">あの敗北から…何かがおかしい気がする</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.ojousama.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5411,29 +5411,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.ojousama.normal[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">光栄でございます。また精進いたします</t>
+          <t xml:space="preserve">体は治ったのに…動けない……なぜ？</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5443,29 +5443,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.normal[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年を通して成長できましたこと、皆さまのおかげです</t>
+          <t xml:space="preserve">リングに戻れたというのに…怖いわ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5475,29 +5475,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.normal[1]</t>
+          <t xml:space="preserve">penalty_end.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさかわたくしがこのような栄誉に…。先輩方の背中、しかと見ておりました</t>
+          <t xml:space="preserve">怪我は癒えましたのに…気力が戻らないわね</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.ojousama.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5522,14 +5522,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この栄冠は、わたくしたち二人の信頼が結んだものですわ。</t>
+          <t xml:space="preserve">我が団体の誇りを、この対抗戦で示せましたわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5554,14 +5554,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームのリングに立てますこと、身に余る光栄ですわ</t>
+          <t xml:space="preserve">あのような激闘、生涯忘れませんわ。対戦してくれたお相手に、心より敬意を</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このような大舞台、夢にまで見ましたのよ</t>
+          <t xml:space="preserve">この王座をお預かりしている限り、最高の試合をお約束いたします</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[3]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5618,14 +5618,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日を、生涯忘れませんわ</t>
+          <t xml:space="preserve">華やかな舞台から降りる日が来たということ。…でも、後悔はございません</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">mediaAward.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5650,14 +5650,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員御礼、まさに奇跡のような景色ですわ…</t>
+          <t xml:space="preserve">光栄でございます。また精進いたします</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">mvp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5682,14 +5682,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の熱気、今も胸に残っておりますの</t>
+          <t xml:space="preserve">一年を通して成長できましたこと、皆さまのおかげです</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[3]</t>
+          <t xml:space="preserve">rookie.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5714,14 +5714,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この日のこと、生涯の誇りとしますわ</t>
+          <t xml:space="preserve">まさかわたくしがこのような栄誉に…。先輩方の背中、しかと見ておりました</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5731,29 +5731,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.normal[1]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">稽古が楽しくなってまいりました</t>
+          <t xml:space="preserve">この栄冠は、わたくしたち二人の信頼が結んだものですわ。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5763,29 +5763,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しずつ、体が応えてくれるようになってきたわね</t>
+          <t xml:space="preserve">ドームのリングに立てますこと、身に余る光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い仲間に恵まれたわね</t>
+          <t xml:space="preserve">このような大舞台、夢にまで見ましたのよ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5827,29 +5827,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少々疲れが出たようで…次までには整えます</t>
+          <t xml:space="preserve">今日という日を、生涯忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5859,29 +5859,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様からこれほどの声援をいただけるのは、光栄です</t>
+          <t xml:space="preserve">満員御礼、まさに奇跡のような景色ですわ…</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5891,29 +5891,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう結構ですわ</t>
+          <t xml:space="preserve">お客様の熱気、今も胸に残っておりますの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5923,29 +5923,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、考え事がございまして</t>
+          <t xml:space="preserve">この日のこと、生涯の誇りとしますわ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.ojousama.normal[1]</t>
+          <t xml:space="preserve">N1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5970,14 +5970,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お金のことで文句を言うつもりはないけれど</t>
+          <t xml:space="preserve">稽古が楽しくなってまいりました</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5987,29 +5987,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.ojousama.normal[1]</t>
+          <t xml:space="preserve">N1.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ。……わたくし、この程度に見られていましたのね</t>
+          <t xml:space="preserve">少しずつ、体が応えてくれるようになってきたわね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6019,29 +6019,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.ojousama.normal[1]</t>
+          <t xml:space="preserve">N2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、ありがとうございます。大切に使わせていただきます</t>
+          <t xml:space="preserve">良い仲間に恵まれたわね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6051,29 +6051,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.ojousama.normal[1]</t>
+          <t xml:space="preserve">N3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿ですの？ 精一杯取り組みますわ</t>
+          <t xml:space="preserve">少々疲れが出たようで…次までには整えます</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6083,29 +6083,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.ojousama.normal[1]</t>
+          <t xml:space="preserve">N4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見守ってくださったんですのね…その気持ちに、お応えしなくては</t>
+          <t xml:space="preserve">皆様からこれほどの声援をいただけるのは、光栄です</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6115,29 +6115,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.ojousama.normal[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。もう少し、頑張ってみます</t>
+          <t xml:space="preserve">…もう結構ですわ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6147,29 +6147,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.ojousama.normal[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアのお仕事ですの？ 精一杯務めます</t>
+          <t xml:space="preserve">…少し、考え事がございまして</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6179,29 +6179,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.ojousama.normal[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しいお時間でしたわ。それでは、ごきげんよう</t>
+          <t xml:space="preserve">…お金のことで文句を言うつもりはないけれど</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.ojousama.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6226,14 +6226,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。リフレッシュして戻って参ります</t>
+          <t xml:space="preserve">まあ。……わたくし、この程度に見られていましたのね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.ojousama.normal[1]</t>
+          <t xml:space="preserve">bonus.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…そこまでしてくださるなんて。早く戻りますわ</t>
+          <t xml:space="preserve">まあ、ありがとうございます。大切に使わせていただきます</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.ojousama.normal[1]</t>
+          <t xml:space="preserve">camp.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯、学ばせていただきます</t>
+          <t xml:space="preserve">合宿ですの？ 精一杯取り組みますわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6322,14 +6322,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアのお話ですの？ ぜひお受けしたいですわ</t>
+          <t xml:space="preserve">ずっと見守ってくださったんですのね…その気持ちに、お応えしなくては</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.ojousama.normal[1]</t>
+          <t xml:space="preserve">encourage.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6354,14 +6354,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しいスカウトのお話が、届いているそうです</t>
+          <t xml:space="preserve">…ありがとうございます。もう少し、頑張ってみます</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.ojousama.normal[1]</t>
+          <t xml:space="preserve">media.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からお話がございましたの…</t>
+          <t xml:space="preserve">メディアのお仕事ですの？ 精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.normal[1]</t>
+          <t xml:space="preserve">party.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6418,14 +6418,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はお稽古をお休みさせていただきますわ…理由は…ご想像にお任せしますわ</t>
+          <t xml:space="preserve">楽しいお時間でしたわ。それでは、ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.ojousama.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6450,14 +6450,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（控室で「あの方の采配、少しおかしくなくて？」と囁いている）</t>
+          <t xml:space="preserve">ありがとうございます。リフレッシュして戻って参ります</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.ojousama.normal[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「窮屈な場所からは、いつでも出ていけますの」と投稿）</t>
+          <t xml:space="preserve">まあ…そこまでしてくださるなんて。早く戻りますわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.ojousama.normal[1]</t>
+          <t xml:space="preserve">trainer.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王座への挑戦をお許しいただけませんこと？</t>
+          <t xml:space="preserve">精一杯、学ばせていただきます</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.ojousama.normal[1]</t>
+          <t xml:space="preserve">E1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方との決着を、お許しいただけませんか？</t>
+          <t xml:space="preserve">メディアのお話ですの？ ぜひお受けしたいですわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.ojousama.normal[1]</t>
+          <t xml:space="preserve">E4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6578,14 +6578,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお休みをいただけますかしら…</t>
+          <t xml:space="preserve">新しいスカウトのお話が、届いているそうです</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.ojousama.normal[1]</t>
+          <t xml:space="preserve">E6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6610,14 +6610,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは困ります！お話し合いをさせてくださいまし</t>
+          <t xml:space="preserve">他の団体からお話がございましたの…</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.ojousama.normal[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…申し上げたいことは、ございます。けれど、口にはできません）</t>
+          <t xml:space="preserve">今日はお稽古をお休みさせていただきますわ…理由は…ご想像にお任せしますわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.ojousama.normal[1]</t>
+          <t xml:space="preserve">S_grumble.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6674,14 +6674,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓の時間をいただけませんこと？</t>
+          <t xml:space="preserve">（控室で「あの方の采配、少しおかしくなくて？」と囁いている）</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.ojousama.normal[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6706,14 +6706,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩のお世話は、私にお任せください</t>
+          <t xml:space="preserve">（SNSに「窮屈な場所からは、いつでも出ていけますの」と投稿）</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.ojousama.normal[1]</t>
+          <t xml:space="preserve">S1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しお時間をいただくことになりそうですわ…</t>
+          <t xml:space="preserve">王座への挑戦をお許しいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.ojousama.normal[1]</t>
+          <t xml:space="preserve">S2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6770,14 +6770,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…もう限界ですわ</t>
+          <t xml:space="preserve">あの方との決着を、お許しいただけませんか？</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.ojousama.normal[1]</t>
+          <t xml:space="preserve">S3.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6802,14 +6802,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちらにも非がおありでしょうに…</t>
+          <t xml:space="preserve">少しお休みをいただけますかしら…</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.ojousama.normal[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6834,14 +6834,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、コラボのお話ですの。嬉しい限りですわ</t>
+          <t xml:space="preserve">このままでは困ります！お話し合いをさせてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.ojousama.normal[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6866,14 +6866,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMですか。しっかりお役目を果たしますわ</t>
+          <t xml:space="preserve">（…申し上げたいことは、ございます。けれど、口にはできません）</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.ojousama.normal[1]</t>
+          <t xml:space="preserve">S5.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6898,14 +6898,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に直接お礼を申し上げる機会ですわね</t>
+          <t xml:space="preserve">特訓の時間をいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.ojousama.normal[1]</t>
+          <t xml:space="preserve">S6.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイですか。精一杯美しく歩いてみせますわ</t>
+          <t xml:space="preserve">後輩のお世話は、私にお任せください</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.ojousama.normal[1]</t>
+          <t xml:space="preserve">B1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6962,14 +6962,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">撮影ですか。美しく仕上げていただけるよう努めますわ</t>
+          <t xml:space="preserve">少しお時間をいただくことになりそうですわ…</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.ojousama.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6994,14 +6994,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ番組ですか。品よくふるまえるよう努めますわ</t>
+          <t xml:space="preserve">あの方とは…もう限界ですわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ojousama.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7026,14 +7026,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材ですか？ 精一杯務めさせていただきます</t>
+          <t xml:space="preserve">あちらにも非がおありでしょうに…</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7043,29 +7043,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
+          <t xml:space="preserve">まあ、コラボのお話ですの。嬉しい限りですわ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7075,29 +7075,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
+          <t xml:space="preserve">CMですか。しっかりお役目を果たしますわ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7107,29 +7107,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">B4_fan.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
+          <t xml:space="preserve">ファンの方々に直接お礼を申し上げる機会ですわね</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7139,29 +7139,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
+          <t xml:space="preserve">ランウェイですか。精一杯美しく歩いてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7171,29 +7171,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
+          <t xml:space="preserve">撮影ですか。美しく仕上げていただけるよう努めますわ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7203,29 +7203,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
+          <t xml:space="preserve">バラエティ番組ですか。品よくふるまえるよう努めますわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7235,29 +7235,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">B4.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
+          <t xml:space="preserve">取材ですか？ 精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7289,7 +7289,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7321,7 +7321,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7353,7 +7353,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7410,14 +7410,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
+          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
+          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.normal[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
+          <t xml:space="preserve">お選びいただけるなら、精一杯努めますわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.normal[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
+          <t xml:space="preserve">よろしくお願いしますわ。精一杯努めますの</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.normal[2]</t>
+          <t xml:space="preserve">draftJoin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7570,14 +7570,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
+          <t xml:space="preserve">お選びいただき、光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7602,14 +7602,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
+          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.normal[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7634,14 +7634,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見つけていただいたからには、お応えするわ。……期待を裏切るつもりはないもの</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。お力になりますの</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7666,14 +7666,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
+          <t xml:space="preserve">よろしくお願いいたしますわ。精一杯務めますの</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.normal[1]</t>
+          <t xml:space="preserve">injury.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7698,14 +7698,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
+          <t xml:space="preserve">このくらい、たいしたことございませんわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">injury.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
+          <t xml:space="preserve">少しだけ休ませてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">release.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7762,14 +7762,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ベルトが、こんなに重いなんて。……確かに、この手で掴んだのね</t>
+          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">release.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
+          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7826,14 +7826,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7858,14 +7858,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
+          <t xml:space="preserve">見つけていただいたからには、お応えするわ。……期待を裏切るつもりはないもの</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7897,7 +7897,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7907,12 +7907,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7929,7 +7929,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7961,7 +7961,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7993,7 +7993,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8003,29 +8003,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう以前のようには戻れませんわ</t>
+          <t xml:space="preserve">お世話になりましたわ。感謝しておりますの</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し距離ができたように感じますわ</t>
+          <t xml:space="preserve">この団体での日々、忘れませんわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8067,29 +8067,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不思議と波長が合いますの。心地よい距離感ですわ</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8099,29 +8099,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">かけがえのない方ですわ。何物にも代えられません</t>
+          <t xml:space="preserve">悔しゅうございますわ…でも、次こそは…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8131,29 +8131,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう過去のことですわ</t>
+          <t xml:space="preserve">防衛いたしましたわ。この座、まだまだ譲りませんの</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8163,29 +8163,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくありませんわ…こんな気持ちは初めて</t>
+          <t xml:space="preserve">ベルトを失いましたわ…でも、ここで終わりではありませんの</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8195,29 +8195,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何としてでも超えてみせますわ</t>
+          <t xml:space="preserve">……ベルトが、こんなに重いなんて。……確かに、この手で掴んだのね</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8242,14 +8242,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの宿命ですわ…それ以外に言葉がない</t>
+          <t xml:space="preserve">もう以前のようには戻れませんわ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8274,14 +8274,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここがわたくしの居場所ですわ。誇りに思います</t>
+          <t xml:space="preserve">少し距離ができたように感じますわ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8306,14 +8306,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このような扱いを受ける覚えはございませんわ</t>
+          <t xml:space="preserve">不思議と波長が合いますの。心地よい距離感ですわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8338,14 +8338,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の運営方針に…疑問を感じますわ</t>
+          <t xml:space="preserve">かけがえのない方ですわ。何物にも代えられません</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.ojousama.normal[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8370,14 +8370,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">敗北は悔しいですけど…素晴らしい試合でした</t>
+          <t xml:space="preserve">もう過去のことですわ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8402,14 +8402,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素晴らしい勝利ですわ。この舞台に相応しい試合でした</t>
+          <t xml:space="preserve">負けたくありませんわ…こんな気持ちは初めて</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.ojousama.normal[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8434,14 +8434,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この敗北…受け入れがたいわね</t>
+          <t xml:space="preserve">何としてでも超えてみせますわ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.ojousama.normal[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8466,14 +8466,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てたわ。……積み上げたものが、出ただけね</t>
+          <t xml:space="preserve">わたくしの宿命ですわ…それ以外に言葉がない</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.ojousama.normal[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8498,14 +8498,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
+          <t xml:space="preserve">ここがわたくしの居場所ですわ。誇りに思います</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.ojousama.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8530,14 +8530,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
+          <t xml:space="preserve">このような扱いを受ける覚えはございませんわ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.ojousama.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.ojousama[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待遇には満足しております</t>
+          <t xml:space="preserve">この団体の運営方針に…疑問を感じますわ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8594,14 +8594,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
+          <t xml:space="preserve">敗北は悔しいですけど…素晴らしい試合でした</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8626,14 +8626,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動向が…気になります</t>
+          <t xml:space="preserve">素晴らしい勝利ですわ。この舞台に相応しい試合でした</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
+          <t xml:space="preserve">この敗北…受け入れがたいわね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8690,14 +8690,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調が…あまり芳しくありません</t>
+          <t xml:space="preserve">勝てたわ。……積み上げたものが、出ただけね</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8722,14 +8722,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
+          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8754,14 +8754,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
+          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8786,14 +8786,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
+          <t xml:space="preserve">待遇には満足しております</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8818,14 +8818,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
+          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8850,14 +8850,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
+          <t xml:space="preserve">動向が…気になります</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8867,29 +8867,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
+          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8899,29 +8899,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
+          <t xml:space="preserve">体調が…あまり芳しくありません</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8931,29 +8931,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
+          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8963,29 +8963,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
+          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8995,29 +8995,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒したわ。…少し息は乱れているけれど。次はどなた？</t>
+          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9027,29 +9027,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.normal[2]</t>
+          <t xml:space="preserve">GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ちきれませんわね。次の方、早くいらして</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9059,29 +9059,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはまいりません</t>
+          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
+          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.normal[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりません</t>
+          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.normal[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞だけでは、わたくし、満足できません。次は三人で勝ちますわ</t>
+          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.normal[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9202,14 +9202,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はもう悲鳴を上げています。ですが……このリングを明け渡す理由にはなりませんの</t>
+          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.normal[2]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9234,14 +9234,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
+          <t xml:space="preserve">一人、倒したわ。…少し息は乱れているけれど。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
+          <t xml:space="preserve">待ちきれませんわね。次の方、早くいらして</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9298,14 +9298,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
+          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはまいりません</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.normal[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9330,14 +9330,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
+          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.normal[2]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
+          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりません</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
+          <t xml:space="preserve">この賞だけでは、わたくし、満足できません。次は三人で勝ちますわ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9426,14 +9426,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次もこの調子で参ります</t>
+          <t xml:space="preserve">身体はもう悲鳴を上げています。ですが……このリングを明け渡す理由にはなりませんの</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9458,14 +9458,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
+          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実りある大会でした</t>
+          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝。全てを出し切ります</t>
+          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
+          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9586,14 +9586,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
+          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
+          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9650,14 +9650,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
+          <t xml:space="preserve">次もこの調子で参ります</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.normal[2]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
+          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9714,14 +9714,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
+          <t xml:space="preserve">実りある大会でした</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9746,14 +9746,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
+          <t xml:space="preserve">決勝。全てを出し切ります</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9778,14 +9778,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
+          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの興行、拝見したわ。……少し、もの足りないわね。私が出れば、変わるはずですもの</t>
+          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9842,14 +9842,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
+          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9874,14 +9874,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
+          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9906,14 +9906,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
+          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9923,12 +9923,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9938,14 +9938,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
+          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9970,14 +9970,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
+          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10002,14 +10002,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
+          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10034,14 +10034,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
+          <t xml:space="preserve">そちらの興行、拝見したわ。……少し、もの足りないわね。私が出れば、変わるはずですもの</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10066,14 +10066,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
+          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10098,14 +10098,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
+          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[3]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10130,14 +10130,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
+          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10147,29 +10147,29 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.normal[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのね…感無量だわ</t>
+          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10179,59 +10179,283 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
+          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[2]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.normal[2]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[2]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.normal[2]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[3]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.normal[3]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られたのね…感無量だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr" s="2">
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr" s="12">
+      <c r="D317" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr" s="2">
+      <c r="E317" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr" s="3">
+      <c r="F317" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見つけていただいたからには、お応えするわ。……期待を裏切るつもりはないもの</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H310"/>
+  <autoFilter ref="A1:H317"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H310"/>
+  <dimension ref="A1:H312"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8473,7 +8473,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8498,14 +8498,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
+          <t xml:space="preserve">あの方と同じ空間にいるだけで、集中が乱れますわ…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8530,14 +8530,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
+          <t xml:space="preserve">…今日もあの顔が頭をよぎった。本当に、困ります</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-02.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待遇には満足しております</t>
+          <t xml:space="preserve">今日のトレーニングも充実したものになりました</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8594,14 +8594,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
+          <t xml:space="preserve">最近の扱いに…少々不満がございます</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8626,14 +8626,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動向が…気になります</t>
+          <t xml:space="preserve">待遇には満足しております</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-04.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8658,14 +8658,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
+          <t xml:space="preserve">一緒の時間、わたくしにとって大切です</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-05.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8690,14 +8690,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調が…あまり芳しくありません</t>
+          <t xml:space="preserve">動向が…気になります</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-06.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8722,14 +8722,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
+          <t xml:space="preserve">わたくしを出場させない理由があるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-07.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8754,14 +8754,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
+          <t xml:space="preserve">体調が…あまり芳しくありません</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-08.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8786,14 +8786,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
+          <t xml:space="preserve">連敗…こんなはずでは…ないのに</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-09.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8818,14 +8818,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
+          <t xml:space="preserve">連勝ですわ。わたくしの実力が証明されたわね</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-10.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8850,14 +8850,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
+          <t xml:space="preserve">この弱い体が恨めしい…早くリングに</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8867,29 +8867,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">GL-11.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
+          <t xml:space="preserve">存じ上げてはおりますけれど、関心はございません</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8899,29 +8899,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
+          <t xml:space="preserve">好調期は過ぎたようですけど…よい経験でしたわ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8946,14 +8946,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
+          <t xml:space="preserve">身体はもう悲鳴を上げていますわ。ですが…最後の舞台、退くわけには参りませんの</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8978,14 +8978,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
+          <t xml:space="preserve">ここまで傷だらけですけれど。この一戦で、全て決まりますのよ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.normal[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9010,14 +9010,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒したわ。…少し息は乱れているけれど。次はどなた？</t>
+          <t xml:space="preserve">どなたが来ようと、この場所は明け渡しませんわ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.normal[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9042,14 +9042,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ちきれませんわね。次の方、早くいらして</t>
+          <t xml:space="preserve">お相手が誰であれ、覚悟してお越しなさいまし</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはまいりません</t>
+          <t xml:space="preserve">一人、倒したわ。…少し息は乱れているけれど。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">survivor.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
+          <t xml:space="preserve">待ちきれませんわね。次の方、早くいらして</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.normal[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりません</t>
+          <t xml:space="preserve">三人で掴んだ勝利ですわ。わたくし一人では、こうはまいりません</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.normal[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞だけでは、わたくし、満足できません。次は三人で勝ちますわ</t>
+          <t xml:space="preserve">お二人が繋いでくださったから、わたくしがここに立てていますの</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.normal[1]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9202,14 +9202,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はもう悲鳴を上げています。ですが……このリングを明け渡す理由にはなりませんの</t>
+          <t xml:space="preserve">お褒めいただけるのは光栄ですわ。ですが……団体が負けたという事実は、変わりません</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.normal[2]</t>
+          <t xml:space="preserve">defiant.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9234,14 +9234,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
+          <t xml:space="preserve">この賞だけでは、わたくし、満足できません。次は三人で勝ちますわ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
+          <t xml:space="preserve">身体はもう悲鳴を上げています。ですが……このリングを明け渡す理由にはなりませんの</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.normal[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9298,14 +9298,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
+          <t xml:space="preserve">何人お相手したか、数えるのも野暮ですわね。わたくしは最後まで立っていた、それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.normal[1]</t>
+          <t xml:space="preserve">champion.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9330,14 +9330,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
+          <t xml:space="preserve">優勝。応援してくださった皆様のおかげです</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.normal[2]</t>
+          <t xml:space="preserve">champion.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9362,14 +9362,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
+          <t xml:space="preserve">この優勝を糧に、さらに上を目指します</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9394,14 +9394,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
+          <t xml:space="preserve">不甲斐ない結果でした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">postLose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9426,14 +9426,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次もこの調子で参ります</t>
+          <t xml:space="preserve">悔しい…。もっと練習しなくては…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9458,14 +9458,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
+          <t xml:space="preserve">ひとつ勝ちました。でも油断は禁物ね</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実りある大会でした</t>
+          <t xml:space="preserve">次もこの調子で参ります</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9522,14 +9522,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝。全てを出し切ります</t>
+          <t xml:space="preserve">収穫の多い大会でしたわ。次はもっと上を目指します</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
+          <t xml:space="preserve">postWin.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
+          <t xml:space="preserve">実りある大会でした</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9586,14 +9586,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
+          <t xml:space="preserve">決勝。全てを出し切ります</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
+          <t xml:space="preserve">ここまで来ましたのだから。最後まで、私らしく</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.normal[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9650,14 +9650,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
+          <t xml:space="preserve">お相手がどなたであれ、全力を尽くします</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.normal[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
+          <t xml:space="preserve">わたくしの試合を、ご覧に入れます</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">summon.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9714,14 +9714,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
+          <t xml:space="preserve">選出されましたわ。しっかりやりますわよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">summon.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9746,14 +9746,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
+          <t xml:space="preserve">この大会で、私の実力を知らしめましょうか</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9778,14 +9778,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
+          <t xml:space="preserve">本日は負けるわけにはまいりません</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの興行、拝見したわ。……少し、もの足りないわね。私が出れば、変わるはずですもの</t>
+          <t xml:space="preserve">……勝ちましたわ。この大舞台で……最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
@@ -9842,14 +9842,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
+          <t xml:space="preserve">わたくしの力、ようやく証明できましたわね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
@@ -9874,14 +9874,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
+          <t xml:space="preserve">そちらの興行、拝見したわ。……少し、もの足りないわね。私が出れば、変わるはずですもの</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
@@ -9906,14 +9906,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
+          <t xml:space="preserve">わたくしたちの実力をお見せする良い機会ですわ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9923,12 +9923,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9938,14 +9938,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
+          <t xml:space="preserve">あら、お逃げになるの？ 残念ですわ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.normal[2]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9970,14 +9970,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
+          <t xml:space="preserve">…お覚悟が足りないようですわね</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.normal[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10002,14 +10002,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
+          <t xml:space="preserve">負けてしまいましたわ…。でも、次こそは</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.normal[2]</t>
+          <t xml:space="preserve">result_lose.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10034,14 +10034,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
+          <t xml:space="preserve">悔しいですわ…。でも、この経験を糧にいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">result_win.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10066,14 +10066,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
+          <t xml:space="preserve">わたくしたちの勝利ですわ。誇らしいですわね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[2]</t>
+          <t xml:space="preserve">result_win.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10098,14 +10098,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
+          <t xml:space="preserve">いい対抗戦でしたわ。またの機会を楽しみにしておりますわ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[3]</t>
+          <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10130,14 +10130,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
+          <t xml:space="preserve">わたくしたちの実力、お分かりいただけたかしら？</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10147,29 +10147,29 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのね…感無量だわ</t>
+          <t xml:space="preserve">団体の名誉は守りましたわ。当然のことですけれど</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.normal[3]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10179,59 +10179,123 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.normal[1]</t>
+          <t xml:space="preserve">ojousama.normal[3]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
+          <t xml:space="preserve">団体の名に恥じない勝利でしたわ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られたのね…感無量だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.normal[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけていただいたこと、感謝しています。……ここで、また一から積み上げていくわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr" s="2">
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr" s="12">
+      <c r="D312" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.normal[1]</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr" s="2">
+      <c r="E312" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr" s="3">
+      <c r="F312" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見つけていただいたからには、お応えするわ。……期待を裏切るつもりはないもの</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H310"/>
+  <autoFilter ref="A1:H312"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×ノーマル.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、わたくし、あの方と対戦したいのです。</t>
+          <t xml:space="preserve">社長、わたくしたち三人で、あちらへ挑みたいのです。</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあります。あの方と試合をさせてくださいませ</t>
+          <t xml:space="preserve">お願いがあります。三人であちらへ挑ませてくださいませ。</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不躾を承知で申します。あの方と当たりたいのです。</t>
+          <t xml:space="preserve">不躾を承知で申します。三人であちらへ参りたいのです。</t>
         </is>
       </c>
     </row>
